--- a/apps/web/public/samples/QuoteLens-sample-BOM.xlsx
+++ b/apps/web/public/samples/QuoteLens-sample-BOM.xlsx
@@ -2968,7 +2968,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>3 blockers stop the quote. Every risk explains why, with evidence.</t>
+          <t>Blockers stop the quote (F1 and J2 always; obsolete parts depend on the market). Every risk explains why, with evidence.</t>
         </is>
       </c>
     </row>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>F1: enter a part number. J2: correct the quantity. Hall sensor U11-U13: Find alternates and approve the drop-in.</t>
+          <t>F1: enter a part number. J2: correct the quantity. An obsolete part: Find alternates and approve a drop-in, or waive it with a reason.</t>
         </is>
       </c>
     </row>
@@ -3035,7 +3035,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Prices, stock and lifecycle come from the QuoteLens demo catalog (synthetic values).</t>
+          <t>Prices, stock and lifecycle are fetched live from DigiKey, Mouser and element14, so remarks about the market may differ from today's data.</t>
         </is>
       </c>
       <c r="B15" s="4" t="n"/>
